--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260604.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260604.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>147,765</t>
+          <t>161,765</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>30.53%</t>
+          <t>27.45%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>1,070,586,655</t>
+          <t>1,150,404,096</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>14.68%</t>
+          <t>14.81%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>107,270</t>
+          <t>117,460</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>10.65%</t>
+          <t>11.25%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>54,555</t>
+          <t>59,655</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>7.65%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>16,755</t>
+          <t>18,435</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.93%</t>
+          <t>7.20%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>129,695</t>
+          <t>142,195</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>4.94%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>63,880</t>
+          <t>69,830</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.38%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>6,105</t>
+          <t>6,715</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>70,155</t>
+          <t>76,815</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>48,455</t>
+          <t>53,055</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>21,155</t>
+          <t>23,165</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>19,603</t>
+          <t>21,463</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>82,885</t>
+          <t>90,385</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>33,820</t>
+          <t>37,030</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>21,755</t>
+          <t>23,825</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -941,100 +941,100 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>54,855</t>
+          <t>60,065</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>20,870</t>
+          <t>13,731</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>12,541</t>
+          <t>22,920</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>8,580</t>
+          <t>31,228</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>28,428</t>
+          <t>9,400</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>38,810</t>
+          <t>42,560</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
@@ -1073,51 +1073,51 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>63,568</t>
+          <t>69,818</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,530,860</t>
+          <t>25,098</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>22,918</t>
+          <t>149,115</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,167</t>
+          <t>23,177</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,88 +1151,88 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>135,615</t>
+          <t>11,326</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>10,346</t>
+          <t>21,705</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>19,805</t>
+          <t>18,721</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>17,071</t>
+          <t>44,150</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1249,29 +1249,29 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>12,645</t>
+          <t>13,845</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>40,300</t>
+          <t>50,760</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,29 +1283,29 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>46,360</t>
+          <t>1,559,570</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>RDI_NTD</t>
+          <t>RDI_USD</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1315,32 +1315,10 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>31,460,000</t>
+          <t>698,253</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>RDI_USD</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>28,710</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
